--- a/data/export/2026-10-23-浦东35路.xlsx
+++ b/data/export/2026-10-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1339 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东35路.xlsx
+++ b/data/export/2026-10-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,20 +436,20 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -965,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -998,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1108,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq38，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1109,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1117,10 +1149,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1159,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1318,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1429,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1540,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1651,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1762,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1873,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1934,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1984,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2045,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2095,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2156,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2206,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2267,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2317,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2378,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2428,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2489,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2539,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2600,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2650,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2711,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2761,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2822,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2824,7 +2872,1129 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A62773D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东35路.xlsx
+++ b/data/export/2026-10-23-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -761,19 +761,19 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq38，推进9站，达到≥2站确认条件</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq42，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3324,22 +3324,22 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3435,22 +3435,22 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3502,7 +3502,7 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       <c r="T29" s="2" t="inlineStr"/>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3954,7 +3954,7 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">

--- a/data/export/2026-10-23-浦东35路.xlsx
+++ b/data/export/2026-10-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq42，推进13站，达到≥2站确认条件</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq58，推进29站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1235,32 +1235,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1268,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1292,33 +1296,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1426,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1457,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1490,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1640,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1712,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1751,7 +1767,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1823,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1901,12 +1917,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1934,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1942,10 +1958,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 5分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2045,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2156,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2267,7 +2299,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2378,7 +2410,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,7 +2521,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2632,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2743,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,7 +2854,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2933,7 +2965,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,7 +3076,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3155,7 +3187,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3266,7 +3298,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3377,7 +3409,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3488,7 +3520,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3599,7 +3631,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3710,7 +3742,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3764,7 +3796,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3857,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3940,7 +3972,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3989,12 +4021,801 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>143.0</t>
         </is>
       </c>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>3/27</t>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>5/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东35路.xlsx
+++ b/data/export/2026-10-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1806,32 +1806,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1839,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1863,33 +1867,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1930,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq59，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1950,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2077,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2155,32 +2163,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2188,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2212,33 +2224,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2338,7 +2354,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2377,32 +2393,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2410,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2434,33 +2454,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -2488,32 +2512,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -2521,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2545,33 +2573,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2671,7 +2703,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2710,32 +2742,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2743,7 +2779,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2767,33 +2803,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2893,7 +2933,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2932,32 +2972,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2965,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2989,17 +3033,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3009,13 +3053,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3235,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3226,7 +3274,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3298,7 +3346,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3409,7 +3457,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3520,7 +3568,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3631,7 +3679,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3742,7 +3790,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3796,7 +3844,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3905,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3972,7 +4020,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4026,7 +4074,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4135,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4141,7 +4189,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4250,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4313,7 +4361,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4367,7 +4415,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4476,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4539,7 +4587,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4593,7 +4641,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4702,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4765,7 +4813,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4819,6 +4867,1136 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>12/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>9/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A62773D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-23-浦东35路.xlsx
+++ b/data/export/2026-10-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1431,13 +1431,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1545,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1556,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1728,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1843,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2430,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2484,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2603,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2779,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2833,7 +2837,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -2861,32 +2865,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2894,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2918,17 +2926,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2938,13 +2946,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3048,14 +3060,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -3063,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3235,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3313,32 +3325,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3346,7 +3362,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3370,17 +3386,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3390,13 +3406,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3477,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3535,32 +3555,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3568,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3592,33 +3616,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -3646,32 +3674,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3679,7 +3711,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3703,33 +3735,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3826,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3844,7 +3880,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -3872,32 +3908,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3905,7 +3945,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3929,17 +3969,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3949,17 +3989,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3987,32 +4027,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4020,7 +4064,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4044,37 +4088,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4102,32 +4146,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4135,7 +4183,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4159,37 +4207,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4217,12 +4265,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4250,7 +4298,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4258,10 +4306,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4361,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4415,7 +4479,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -4443,32 +4507,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4476,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4500,17 +4568,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4520,13 +4588,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4659,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4626,7 +4698,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4641,7 +4713,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4774,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4813,7 +4885,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4924,7 +4996,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4978,7 +5050,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5111,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5093,7 +5165,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5226,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5265,7 +5337,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5319,7 +5391,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5452,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5491,7 +5563,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5602,7 +5674,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5656,7 +5728,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5789,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5771,7 +5843,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5904,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5876,13 +5948,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -5890,22 +5966,22 @@
       <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>沪A62773D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -5938,12 +6014,12 @@
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5957,43 +6033,733 @@
       <c r="T48" s="2" t="inlineStr"/>
       <c r="U48" s="2" t="inlineStr">
         <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>5/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A62773D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
           <t>11:20</t>
         </is>
       </c>
-      <c r="V48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W48" s="2" t="inlineStr">
+      <c r="W49" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X48" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y48" s="2" t="inlineStr">
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z48" s="2" t="inlineStr">
+      <c r="Z49" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
+      <c r="AA49" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB48" s="2" t="inlineStr"/>
-      <c r="AC48" s="2" t="inlineStr">
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr">
         <is>
           <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>9/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>8/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>11/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东35路.xlsx
+++ b/data/export/2026-10-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,18 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,13 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2025,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2028,7 +2036,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,18 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2363,13 +2375,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2478,17 +2494,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,7 +2608,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2607,7 +2623,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2718,7 +2734,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2956,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3075,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3202,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3297,7 +3313,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3543,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3646,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3765,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3896,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3999,7 +4015,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4118,7 +4134,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4237,7 +4253,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4286,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4298,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4364,7 +4380,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4392,32 +4408,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4425,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4449,17 +4469,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4469,17 +4489,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4517,24 +4537,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4544,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4593,12 +4613,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4626,32 +4646,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4659,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4683,17 +4707,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4703,17 +4727,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4741,32 +4765,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4774,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4798,33 +4826,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB37" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4852,32 +4884,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4885,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4909,17 +4945,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4929,13 +4965,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4963,32 +5003,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4996,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5020,17 +5064,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5040,17 +5084,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5078,32 +5122,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5111,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5135,17 +5183,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5155,17 +5203,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5193,32 +5241,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5226,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5250,33 +5302,37 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5304,32 +5360,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5337,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5361,17 +5421,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5381,17 +5441,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5419,32 +5479,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5452,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5476,17 +5540,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5496,13 +5560,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5613,7 +5681,7 @@
       <c r="AB44" s="2" t="inlineStr"/>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5713,7 +5781,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5728,7 +5796,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5843,7 +5911,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5958,7 +6026,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6019,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6073,7 +6141,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6202,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6184,7 +6252,7 @@
       <c r="AB49" s="2" t="inlineStr"/>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6313,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6299,7 +6367,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6428,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6414,7 +6482,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6543,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6529,7 +6597,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6590,7 +6658,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6644,7 +6712,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6652,22 +6720,22 @@
       <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6700,12 +6768,12 @@
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6719,47 +6787,725 @@
       <c r="T54" s="2" t="inlineStr"/>
       <c r="U54" s="2" t="inlineStr">
         <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="V54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W54" s="2" t="inlineStr">
+      <c r="W55" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X54" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y54" s="2" t="inlineStr">
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z54" s="2" t="inlineStr">
+      <c r="Z55" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB54" s="2" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>11/27</t>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东35路.xlsx
+++ b/data/export/2026-10-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,14 +2489,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>138.5</t>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2613,17 +2613,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,13 +2728,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,22 +2961,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,22 +3080,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3307,13 +3311,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,14 +3425,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>154.0</t>
@@ -3432,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3647,22 +3655,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3771,7 +3779,7 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3896,7 +3904,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4023,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4119,7 +4127,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4134,7 +4142,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4253,7 +4261,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4737,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4856,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5102,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5332,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5436,14 +5444,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>138.5</t>
@@ -5451,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5598,32 +5606,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5631,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5655,17 +5667,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5675,13 +5687,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5725,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5742,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5766,17 +5786,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5786,17 +5806,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5911,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5939,32 +5959,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5972,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5996,37 +6020,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6054,32 +6078,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6087,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6111,37 +6139,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6169,32 +6197,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6202,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6226,17 +6258,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6246,13 +6278,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB49" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6280,32 +6316,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6313,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6337,37 +6377,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6395,32 +6435,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6428,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6452,17 +6496,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6472,7 +6516,7 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
@@ -6543,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6582,7 +6626,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6597,7 +6641,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6712,7 +6756,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6827,7 +6871,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6932,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6942,7 +6986,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7003,7 +7047,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7114,7 +7158,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7225,7 +7269,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7279,7 +7323,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7340,7 +7384,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7451,7 +7495,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7495,17 +7539,707 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>14/29</t>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东35路.xlsx
+++ b/data/export/2026-10-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4132,17 +4132,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4251,17 +4251,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6326,24 +6326,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6402,12 +6402,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6445,24 +6445,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6554,32 +6554,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6587,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6611,17 +6615,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6631,17 +6635,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6669,32 +6673,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6702,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6726,17 +6734,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6746,17 +6754,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6856,7 +6864,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6932,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7014,12 +7022,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq41，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7047,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7055,10 +7063,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq38（站名待映射） ETA 7分钟参与校验</t>
+        </is>
+      </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -7158,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7269,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7384,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7495,7 +7519,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7610,7 +7634,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7664,7 +7688,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7725,7 +7749,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7840,7 +7864,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7894,7 +7918,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7955,7 +7979,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8004,12 +8028,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8094,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8185,7 +8209,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8229,17 +8253,247 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
           <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东35路.xlsx
+++ b/data/export/2026-10-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2025,18 +2025,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2504,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2623,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3095,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3440,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3670,7 +3674,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3904,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4142,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4256,7 +4260,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4507,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4611,7 +4615,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4626,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4735,17 +4739,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4854,17 +4858,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5340,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5459,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5578,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5701,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5816,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5931,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5996,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6050,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6169,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6407,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6576,12 +6580,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6591,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6645,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6683,24 +6687,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6710,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6759,7 +6763,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6792,32 +6796,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -6825,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6849,17 +6857,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6869,17 +6877,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6907,32 +6915,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6940,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6964,17 +6976,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6984,17 +6996,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7027,7 +7039,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq41，推进3站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq51，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7055,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7149,32 +7161,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7182,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7206,33 +7222,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7347,7 +7367,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7519,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7573,7 +7593,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7688,7 +7708,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7803,7 +7823,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7884,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7918,7 +7938,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7979,7 +7999,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8033,7 +8053,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8114,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8148,7 +8168,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8263,7 +8283,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8324,7 +8344,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8378,7 +8398,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8459,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8483,17 +8503,247 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr">
-        <is>
-          <t>5/29</t>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东35路.xlsx
+++ b/data/export/2026-10-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,14 +1894,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,14 +2259,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>145.0</t>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,14 +5091,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,14 +5210,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>145.0</t>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5453,17 +5453,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5810,17 +5810,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6925,24 +6925,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq51，推进13站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq57，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       <c r="AB56" s="2" t="inlineStr"/>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7171,24 +7171,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7280,32 +7280,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7313,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7337,17 +7341,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7357,7 +7361,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7367,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7478,7 +7482,7 @@
       <c r="AB59" s="2" t="inlineStr"/>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7506,32 +7510,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7539,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7563,17 +7571,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7583,17 +7591,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7621,32 +7629,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7654,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7678,17 +7690,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7698,17 +7710,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7823,7 +7835,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7938,7 +7950,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7999,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8053,7 +8065,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8168,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8283,7 +8295,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8356,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8398,7 +8410,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8471,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8513,7 +8525,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8586,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8628,7 +8640,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8689,7 +8701,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8738,12 +8750,575 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东35路.xlsx
+++ b/data/export/2026-10-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1311,14 +1311,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>142.0</t>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3664,17 +3664,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4136,17 +4136,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,14 +4250,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,14 +4496,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>142.0</t>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6163,17 +6163,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6401,17 +6401,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6639,17 +6639,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6753,14 +6753,14 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7520,24 +7520,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7748,32 +7748,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7781,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7805,17 +7809,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7825,17 +7829,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7863,32 +7867,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7896,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7920,17 +7928,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7940,12 +7948,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7978,32 +7986,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8011,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8035,17 +8047,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8055,17 +8067,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8093,32 +8105,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8126,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8150,17 +8166,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8170,12 +8186,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8208,32 +8224,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8241,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8265,17 +8285,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8285,17 +8305,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8471,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8586,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8701,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8816,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8927,7 +8947,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8981,7 +9001,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9062,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9153,7 +9173,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9211,22 +9231,22 @@
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9259,12 +9279,12 @@
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9278,7 +9298,7 @@
       <c r="T75" s="2" t="inlineStr"/>
       <c r="U75" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="V75" s="2" t="inlineStr">
@@ -9303,22 +9323,1049 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
+      <c r="AA76" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr">
+      <c r="AB76" s="2" t="inlineStr">
         <is>
           <t>145.0</t>
         </is>
       </c>
-      <c r="AC75" s="2" t="inlineStr">
+      <c r="AC76" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A62773D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东35路.xlsx
+++ b/data/export/2026-10-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC84"/>
+  <dimension ref="A1:AC92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1545,14 +1545,14 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>136.3</t>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2030,17 +2030,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,14 +2612,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>137.7</t>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,14 +3084,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>135.7</t>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3204,13 +3204,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3325,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,22 +3433,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3674,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3793,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,7 +3897,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3908,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4092,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4141,12 +4145,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4265,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4457,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4511,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,22 +4619,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,14 +4738,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>136.3</t>
@@ -4749,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,12 +4862,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4933,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5052,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5096,17 +5100,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5225,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,7 +5333,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5463,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5567,7 +5571,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5582,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5701,7 +5705,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5805,14 +5809,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>137.7</t>
@@ -5820,7 +5824,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6158,14 +6162,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>135.7</t>
@@ -6173,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6292,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6530,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6644,12 +6648,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6768,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6877,12 +6881,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6952,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6991,14 +6995,14 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
           <t>136.3</t>
@@ -7006,7 +7010,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7242,17 +7246,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7356,7 +7360,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7432,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7547,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7586,14 +7590,14 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
           <t>137.7</t>
@@ -7601,7 +7605,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7720,7 +7724,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7824,14 +7828,14 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
           <t>135.7</t>
@@ -7839,7 +7843,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7958,7 +7962,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8081,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8115,24 +8119,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8142,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8181,22 +8185,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -8234,24 +8238,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8261,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8310,12 +8314,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8415,7 +8419,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8430,7 +8434,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8458,32 +8462,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8491,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8515,17 +8523,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8535,12 +8543,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8573,32 +8581,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8606,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8630,37 +8642,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8688,32 +8700,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8721,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8745,17 +8761,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8765,17 +8781,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8803,12 +8819,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8836,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8844,10 +8860,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q71" s="2" t="inlineStr"/>
-      <c r="R71" s="2" t="inlineStr"/>
-      <c r="S71" s="2" t="inlineStr"/>
-      <c r="T71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±3分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8914,32 +8946,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8947,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8971,17 +9007,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -8991,17 +9027,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9140,32 +9176,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9173,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9197,17 +9237,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9217,13 +9257,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB74" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9395,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9449,7 +9493,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9621,7 +9665,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9675,7 +9719,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9780,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9790,7 +9834,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9895,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9966,7 +10010,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10020,7 +10064,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10081,7 +10125,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10135,7 +10179,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -10196,7 +10240,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10311,7 +10355,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10365,7 +10409,927 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>136.3</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>137.7</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>135.7</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东35路.xlsx
+++ b/data/export/2026-10-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC92"/>
+  <dimension ref="A1:AC100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>146.3</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2264,17 +2264,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>153.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,14 +2493,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>136.3</t>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2732,17 +2732,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,22 +5095,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>146.3</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5219,17 +5219,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>153.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5452,14 +5452,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>136.3</t>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5695,17 +5695,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7709,14 +7709,14 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>136.3</t>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8591,24 +8591,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8710,24 +8710,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8956,24 +8956,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9022,22 +9022,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>146.3</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9186,24 +9186,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9406,32 +9406,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>171分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9439,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9463,17 +9467,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9483,17 +9487,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>153.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9632,32 +9636,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>176分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9665,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9689,17 +9697,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9709,17 +9717,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9819,7 +9827,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9895,7 +9903,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9934,7 +9942,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10010,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10125,7 +10133,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10240,7 +10248,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10355,7 +10363,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10470,7 +10478,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10524,7 +10532,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10585,7 +10593,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10639,7 +10647,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10708,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10815,7 +10823,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10930,7 +10938,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11045,7 +11053,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11099,7 +11107,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11168,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11209,12 +11217,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -11275,7 +11283,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11329,7 +11337,923 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>136.3</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
           <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr"/>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>148.7</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A62773D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东35路.xlsx
+++ b/data/export/2026-10-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC100"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,22 +2259,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>153.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,22 +3782,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,22 +5214,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>153.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6519,22 +6519,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9406,36 +9406,32 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>171分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9443,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9467,37 +9463,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>153.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9597,7 +9593,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9646,12 +9642,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>176分钟</t>
+          <t>175分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -9673,7 +9669,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9722,7 +9718,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9788,7 +9784,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9842,7 +9838,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9957,7 +9953,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10014,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10100,32 +10096,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10157,37 +10157,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -10823,7 +10823,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10938,7 +10938,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11168,7 +11168,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11398,7 +11398,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -11513,7 +11513,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11567,7 +11567,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11872,7 +11872,7 @@
       <c r="T97" s="2" t="inlineStr"/>
       <c r="U97" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="V97" s="2" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12023,7 +12023,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12084,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -12146,22 +12146,22 @@
       <c r="A100" s="2" t="inlineStr"/>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -12194,12 +12194,12 @@
       <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12213,7 +12213,7 @@
       <c r="T100" s="2" t="inlineStr"/>
       <c r="U100" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="V100" s="2" t="inlineStr">
@@ -12248,12 +12248,353 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>137.3</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr"/>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
           <t>133.0</t>
         </is>
       </c>
-      <c r="AC100" s="2" t="inlineStr">
-        <is>
-          <t>7/30</t>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东35路.xlsx
+++ b/data/export/2026-10-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AC109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1311,22 +1311,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,14 +2965,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>142.7</t>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3438,17 +3438,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>162.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,22 +4500,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4743,17 +4743,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5338,17 +5338,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5571,22 +5571,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5814,17 +5814,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6043,14 +6043,14 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>142.7</t>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6167,17 +6167,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6762,17 +6762,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7000,17 +7000,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7365,17 +7365,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7595,17 +7595,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7833,17 +7833,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7947,14 +7947,14 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
           <t>142.7</t>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8190,17 +8190,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>162.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8553,7 +8553,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9723,7 +9723,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -9981,32 +9981,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>178分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -10014,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10038,37 +10042,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10137,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10187,7 +10191,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10215,32 +10219,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>170分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10248,7 +10256,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10272,37 +10280,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10330,32 +10338,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10363,7 +10375,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10387,17 +10399,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10407,17 +10419,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10445,32 +10457,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10478,7 +10494,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10502,17 +10518,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10522,17 +10538,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10560,32 +10576,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>180分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10593,7 +10613,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10617,17 +10637,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10637,17 +10657,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>162.7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -10675,32 +10695,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10708,7 +10732,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10732,37 +10756,37 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10790,32 +10814,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10823,7 +10851,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10847,17 +10875,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10867,17 +10895,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10905,32 +10933,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10938,7 +10970,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10962,17 +10994,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -10982,17 +11014,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -11053,7 +11085,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11107,7 +11139,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -11168,7 +11200,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11222,7 +11254,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11250,32 +11282,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11283,7 +11319,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11307,17 +11343,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11327,17 +11363,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -11398,7 +11434,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11452,7 +11488,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -11513,7 +11549,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11552,7 +11588,7 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -11567,7 +11603,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11664,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11682,7 +11718,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -11743,7 +11779,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11797,7 +11833,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11894,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11969,7 +12005,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12023,7 +12059,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12120,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12138,7 +12174,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -12199,7 +12235,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12253,7 +12289,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12314,7 +12350,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12368,7 +12404,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -12429,7 +12465,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12540,7 +12576,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12594,7 +12630,697 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>142.7</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr"/>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr"/>
+      <c r="R109" s="2" t="inlineStr"/>
+      <c r="S109" s="2" t="inlineStr"/>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z109" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA109" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB109" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC109" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东35路.xlsx
+++ b/data/export/2026-10-23-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2264,17 +2264,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2732,17 +2732,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3553,13 +3553,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3912,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4150,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4515,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4753,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4991,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5110,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5219,17 +5223,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5457,12 +5461,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5532,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5586,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5695,17 +5699,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5939,7 +5943,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6058,7 +6062,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6480,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6653,7 +6657,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6776,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7014,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7436,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7605,7 +7609,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7714,12 +7718,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7908,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7962,7 +7966,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8323,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8438,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8983,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9037,7 +9041,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9213,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9328,7 +9332,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9372,13 +9376,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB75" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9483,17 +9491,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9669,7 +9677,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9713,17 +9721,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9899,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10018,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10072,7 +10080,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10256,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10310,7 +10318,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10429,7 +10437,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10556,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10786,7 +10794,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -11024,7 +11032,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -11139,7 +11147,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11208,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11549,7 +11557,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11603,7 +11611,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11672,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11746,32 +11754,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11779,7 +11791,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11803,17 +11815,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11823,12 +11835,12 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11861,32 +11873,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11894,7 +11910,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11918,17 +11934,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11938,13 +11954,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB97" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -12005,7 +12025,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12059,7 +12079,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -12087,12 +12107,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq29推进至seq50，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -12120,7 +12140,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12202,32 +12222,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -12235,7 +12259,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12259,17 +12283,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12279,17 +12303,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -12317,12 +12341,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq28推进至seq50，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -12350,7 +12374,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12358,10 +12382,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q101" s="2" t="inlineStr"/>
-      <c r="R101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
       <c r="S101" s="2" t="inlineStr"/>
-      <c r="T101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq24映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12465,7 +12501,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12576,7 +12612,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12658,32 +12694,36 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -12691,7 +12731,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12715,17 +12755,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12735,17 +12775,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12806,7 +12846,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12860,7 +12900,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -12921,7 +12961,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -12975,7 +13015,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -13036,7 +13076,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13090,7 +13130,7 @@
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -13151,7 +13191,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13205,7 +13245,7 @@
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -13266,7 +13306,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -13320,7 +13360,7 @@
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
